--- a/education_forms/047_degmnhs_enrollment_form--education_forms.xlsx
+++ b/education_forms/047_degmnhs_enrollment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>student_type_1</t>
+          <t>student type 1</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>student_type_2</t>
+          <t>student type 2</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>student_type_3</t>
+          <t>student type 3</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>student_type_4</t>
+          <t>student type 4</t>
         </is>
       </c>
     </row>
